--- a/无父体2.0合并表/DRHG2P-1（US）.xlsx
+++ b/无父体2.0合并表/DRHG2P-1（US）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="10" activeTab="11"/>
+    <workbookView windowWidth="28800" windowHeight="11925" firstSheet="10" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="icons" sheetId="8" state="hidden" r:id="rId1"/>
@@ -1630,7 +1630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11457" uniqueCount="3841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11439" uniqueCount="3841">
   <si>
     <t>Language</t>
   </si>
@@ -8579,217 +8579,217 @@
     <t>progressive_discount_value3</t>
   </si>
   <si>
+    <t>Browse Node</t>
+  </si>
+  <si>
+    <t>Browse Path</t>
+  </si>
+  <si>
+    <t>lifting-clamps</t>
+  </si>
+  <si>
+    <t>Industrial &amp; Scientific &gt; Material Handling Products &gt; Pulling &amp; Lifting &gt; Lifting Clamps</t>
+  </si>
+  <si>
     <t>comicbook</t>
   </si>
   <si>
     <t>HX-MOHG1P-CZS-826-1</t>
   </si>
   <si>
+    <t>HX-MOHG1P-CZS-826-2</t>
+  </si>
+  <si>
+    <t>HX-MOHG1P-CZS-826-3</t>
+  </si>
+  <si>
+    <t>HX-MOHG1P-CZS-826-4</t>
+  </si>
+  <si>
+    <t>HX-MOHG1P-CZS-826-5</t>
+  </si>
+  <si>
+    <t>HX-MOHG1P-CZS-826-6</t>
+  </si>
+  <si>
+    <t>CONDITION_LIST_0</t>
+  </si>
+  <si>
+    <t>CONDITION_LIST_1</t>
+  </si>
+  <si>
+    <t>CONDITION_LIST_2</t>
+  </si>
+  <si>
+    <t>CONDITION_LIST_3</t>
+  </si>
+  <si>
+    <t>Lithium</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>GHS</t>
+  </si>
+  <si>
+    <t>Lithium-Air</t>
+  </si>
+  <si>
+    <t>Lithium-Cobalt</t>
+  </si>
+  <si>
+    <t>Lithium Ion</t>
+  </si>
+  <si>
+    <t>lithium_manganese_dioxide</t>
+  </si>
+  <si>
+    <t>lithium_metal</t>
+  </si>
+  <si>
+    <t>Lithium-Nickel Cobalt Aluminum (NCA)</t>
+  </si>
+  <si>
+    <t>Lithium-Nickel Manganese Cobalt (NMC)</t>
+  </si>
+  <si>
+    <t>Lithium-Phosphate</t>
+  </si>
+  <si>
+    <t>Lithium Polymer</t>
+  </si>
+  <si>
+    <t>Lithium-Thionyl Chloride (Li-SOCL2)</t>
+  </si>
+  <si>
+    <t>Lithium-Titanate</t>
+  </si>
+  <si>
+    <t>hardwareclampvise</t>
+  </si>
+  <si>
+    <t>Aisihai</t>
+  </si>
+  <si>
+    <t>AMHLO</t>
+  </si>
+  <si>
+    <t>AMVOOM</t>
+  </si>
+  <si>
+    <t>RUICHENXI</t>
+  </si>
+  <si>
+    <t>GESUNDHEIT</t>
+  </si>
+  <si>
+    <t>Gesundheit</t>
+  </si>
+  <si>
+    <t>Dorypal</t>
+  </si>
+  <si>
+    <t>Uandear</t>
+  </si>
+  <si>
+    <t>youmotu</t>
+  </si>
+  <si>
+    <t>IT-Karmon</t>
+  </si>
+  <si>
+    <t>gotowoco</t>
+  </si>
+  <si>
+    <t>Erectogen</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>Coolpop</t>
+  </si>
+  <si>
+    <t>ROSUN</t>
+  </si>
+  <si>
+    <t>Product ID Type - [ hardwareclampvise ]</t>
+  </si>
+  <si>
+    <t>GTIN</t>
+  </si>
+  <si>
+    <t>EAN</t>
+  </si>
+  <si>
+    <t>GCID</t>
+  </si>
+  <si>
+    <t>ASIN</t>
+  </si>
+  <si>
+    <t>Parentage - [ hardwareclampvise ]</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>Relationship Type - [ hardwareclampvise ]</t>
+  </si>
+  <si>
+    <t>Variation Theme - [ hardwareclampvise ]</t>
+  </si>
+  <si>
+    <t>ColorName</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>ItemPackageQuantity</t>
+  </si>
+  <si>
+    <t>ItemPackageQuantityColor</t>
+  </si>
+  <si>
+    <t>ItemPackageQuantitySize</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>MaterialSize</t>
+  </si>
+  <si>
+    <t>PatternName</t>
+  </si>
+  <si>
+    <t>SizeName</t>
+  </si>
+  <si>
+    <t>SizeName-ColorName</t>
+  </si>
+  <si>
+    <t>Style</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>color-size</t>
+  </si>
+  <si>
+    <t>stylename-size</t>
+  </si>
+  <si>
+    <t>Update Delete - [ hardwareclampvise ]</t>
+  </si>
+  <si>
     <t>PartialUpdate</t>
-  </si>
-  <si>
-    <t>HX-MOHG1P-CZS-826-2</t>
-  </si>
-  <si>
-    <t>HX-MOHG1P-CZS-826-3</t>
-  </si>
-  <si>
-    <t>HX-MOHG1P-CZS-826-4</t>
-  </si>
-  <si>
-    <t>HX-MOHG1P-CZS-826-5</t>
-  </si>
-  <si>
-    <t>HX-MOHG1P-CZS-826-6</t>
-  </si>
-  <si>
-    <t>Browse Node</t>
-  </si>
-  <si>
-    <t>Browse Path</t>
-  </si>
-  <si>
-    <t>lifting-clamps</t>
-  </si>
-  <si>
-    <t>Industrial &amp; Scientific &gt; Material Handling Products &gt; Pulling &amp; Lifting &gt; Lifting Clamps</t>
-  </si>
-  <si>
-    <t>CONDITION_LIST_0</t>
-  </si>
-  <si>
-    <t>CONDITION_LIST_1</t>
-  </si>
-  <si>
-    <t>CONDITION_LIST_2</t>
-  </si>
-  <si>
-    <t>CONDITION_LIST_3</t>
-  </si>
-  <si>
-    <t>Lithium</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>GHS</t>
-  </si>
-  <si>
-    <t>Lithium-Air</t>
-  </si>
-  <si>
-    <t>Lithium-Cobalt</t>
-  </si>
-  <si>
-    <t>Lithium Ion</t>
-  </si>
-  <si>
-    <t>lithium_manganese_dioxide</t>
-  </si>
-  <si>
-    <t>lithium_metal</t>
-  </si>
-  <si>
-    <t>Lithium-Nickel Cobalt Aluminum (NCA)</t>
-  </si>
-  <si>
-    <t>Lithium-Nickel Manganese Cobalt (NMC)</t>
-  </si>
-  <si>
-    <t>Lithium-Phosphate</t>
-  </si>
-  <si>
-    <t>Lithium Polymer</t>
-  </si>
-  <si>
-    <t>Lithium-Thionyl Chloride (Li-SOCL2)</t>
-  </si>
-  <si>
-    <t>Lithium-Titanate</t>
-  </si>
-  <si>
-    <t>hardwareclampvise</t>
-  </si>
-  <si>
-    <t>Aisihai</t>
-  </si>
-  <si>
-    <t>AMHLO</t>
-  </si>
-  <si>
-    <t>AMVOOM</t>
-  </si>
-  <si>
-    <t>RUICHENXI</t>
-  </si>
-  <si>
-    <t>GESUNDHEIT</t>
-  </si>
-  <si>
-    <t>Gesundheit</t>
-  </si>
-  <si>
-    <t>Dorypal</t>
-  </si>
-  <si>
-    <t>Uandear</t>
-  </si>
-  <si>
-    <t>youmotu</t>
-  </si>
-  <si>
-    <t>IT-Karmon</t>
-  </si>
-  <si>
-    <t>gotowoco</t>
-  </si>
-  <si>
-    <t>Erectogen</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>Coolpop</t>
-  </si>
-  <si>
-    <t>ROSUN</t>
-  </si>
-  <si>
-    <t>Product ID Type - [ hardwareclampvise ]</t>
-  </si>
-  <si>
-    <t>GTIN</t>
-  </si>
-  <si>
-    <t>EAN</t>
-  </si>
-  <si>
-    <t>GCID</t>
-  </si>
-  <si>
-    <t>ASIN</t>
-  </si>
-  <si>
-    <t>Parentage - [ hardwareclampvise ]</t>
-  </si>
-  <si>
-    <t>Parent</t>
-  </si>
-  <si>
-    <t>Child</t>
-  </si>
-  <si>
-    <t>Relationship Type - [ hardwareclampvise ]</t>
-  </si>
-  <si>
-    <t>Variation Theme - [ hardwareclampvise ]</t>
-  </si>
-  <si>
-    <t>ColorName</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>ItemPackageQuantity</t>
-  </si>
-  <si>
-    <t>ItemPackageQuantityColor</t>
-  </si>
-  <si>
-    <t>ItemPackageQuantitySize</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>MaterialSize</t>
-  </si>
-  <si>
-    <t>PatternName</t>
-  </si>
-  <si>
-    <t>SizeName</t>
-  </si>
-  <si>
-    <t>SizeName-ColorName</t>
-  </si>
-  <si>
-    <t>Style</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>color-size</t>
-  </si>
-  <si>
-    <t>stylename-size</t>
-  </si>
-  <si>
-    <t>Update Delete - [ hardwareclampvise ]</t>
   </si>
   <si>
     <t>Delete</t>
@@ -14183,16 +14183,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <color indexed="39"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color indexed="63"/>
+      <sz val="1"/>
       <name val="Verdana"/>
       <charset val="134"/>
     </font>
@@ -14200,35 +14191,6 @@
       <b/>
       <sz val="8"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="1"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="63"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Verdana"/>
       <charset val="134"/>
     </font>
     <font>
@@ -14245,14 +14207,52 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="8"/>
+      <name val="Verdana"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="8"/>
+      <name val="Verdana"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <name val="Verdana"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Verdana"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color indexed="63"/>
+      <name val="Verdana"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color indexed="63"/>
+      <name val="Verdana"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color indexed="39"/>
       <name val="Verdana"/>
       <charset val="134"/>
     </font>
@@ -30409,15 +30409,9 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:24">
-      <c r="A4" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>2110</v>
-      </c>
-      <c r="F4" s="25">
-        <v>1</v>
-      </c>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
       <c r="I4" s="25"/>
@@ -30435,20 +30429,12 @@
       <c r="U4" s="25"/>
       <c r="V4" s="25"/>
       <c r="W4" s="25"/>
-      <c r="X4" s="25" t="s">
-        <v>2111</v>
-      </c>
+      <c r="X4" s="25"/>
     </row>
     <row r="5" customHeight="1" spans="1:24">
-      <c r="A5" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>2112</v>
-      </c>
-      <c r="F5" s="25">
-        <v>1</v>
-      </c>
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
@@ -30466,65 +30452,31 @@
       <c r="U5" s="25"/>
       <c r="V5" s="25"/>
       <c r="W5" s="25"/>
-      <c r="X5" s="25" t="s">
-        <v>2111</v>
-      </c>
+      <c r="X5" s="25"/>
     </row>
     <row r="6" customHeight="1" spans="1:24">
-      <c r="A6" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>2113</v>
-      </c>
-      <c r="F6" s="25">
-        <v>1</v>
-      </c>
-      <c r="X6" s="25" t="s">
-        <v>2111</v>
-      </c>
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="F6" s="25"/>
+      <c r="X6" s="25"/>
     </row>
     <row r="7" customHeight="1" spans="1:24">
-      <c r="A7" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>2114</v>
-      </c>
-      <c r="F7" s="25">
-        <v>1</v>
-      </c>
-      <c r="X7" s="25" t="s">
-        <v>2111</v>
-      </c>
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="F7" s="25"/>
+      <c r="X7" s="25"/>
     </row>
     <row r="8" customHeight="1" spans="1:24">
-      <c r="A8" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>2115</v>
-      </c>
-      <c r="F8" s="25">
-        <v>1</v>
-      </c>
-      <c r="X8" s="25" t="s">
-        <v>2111</v>
-      </c>
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="F8" s="25"/>
+      <c r="X8" s="25"/>
     </row>
     <row r="9" customHeight="1" spans="1:24">
-      <c r="A9" s="17" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>2116</v>
-      </c>
-      <c r="F9" s="25">
-        <v>1</v>
-      </c>
-      <c r="X9" s="25" t="s">
-        <v>2111</v>
-      </c>
+      <c r="A9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="F9" s="25"/>
+      <c r="X9" s="25"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteColumns="0" deleteRows="0"/>
@@ -35172,10 +35124,10 @@
     <dataValidation allowBlank="1" showInputMessage="1" prompt="A alpha-numeric 13 digit code. Code identifying standard material items of supply as defined by NATO" sqref="HC3"/>
     <dataValidation allowBlank="1" showInputMessage="1" prompt="An 8 digit code A numeric code classifying products according to the UNSPSC system" sqref="HD3"/>
     <dataValidation allowBlank="1" showInputMessage="1" prompt="&quot;&quot;delete business_price&quot;&quot; (without the quotes)" sqref="HE3"/>
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="G4:S4 B10:B1048576 D4:D1048576 F4:F9 F10:F1048576 U4:U1048576 AM4:AM1048576 BB4:BB1048576 BF4:BF1048576 CA4:CA1048576 CJ4:CJ1048576 CT4:CT1048576 DG4:DG1048576 DL4:DL1048576 EK4:EK1048576 FL4:FL1048576 G5:S1048576 Y4:Z1048576 AQ4:AR1048576 BU4:BV1048576 AB4:AC1048576 AT4:AU1048576 AE4:AK1048576 BK4:BR1048576 CD4:CG1048576 DN4:DQ1048576 CO4:CR1048576 DU4:DX1048576 DA4:DE1048576 EG4:EI1048576 FA4:FC1048576 FE4:FJ1048576 FQ4:GJ1048576 GL4:GU1048576 GW4:HD1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A10:A1048576">
       <formula1>feed_product_type</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="B10:B1048576 D4:D1048576 U4:U1048576 AM4:AM1048576 BB4:BB1048576 BF4:BF1048576 CA4:CA1048576 CJ4:CJ1048576 CT4:CT1048576 DG4:DG1048576 DL4:DL1048576 EK4:EK1048576 FL4:FL1048576 F4:S1048576 Y4:Z1048576 AQ4:AR1048576 BU4:BV1048576 AB4:AC1048576 AT4:AU1048576 AE4:AK1048576 BK4:BR1048576 CD4:CG1048576 DN4:DQ1048576 CO4:CR1048576 DU4:DX1048576 DA4:DE1048576 EG4:EI1048576 FA4:FC1048576 FE4:FJ1048576 FQ4:GJ1048576 GL4:GU1048576 GW4:HD1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C4:C1048576">
       <formula1>brand_name</formula1>
     </dataValidation>
@@ -35191,7 +35143,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="W4:W1048576">
       <formula1>INDIRECT(SUBSTITUTE(A4,"-","_")&amp;"variation_theme")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X4:X9 X10:X1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X4:X1048576">
       <formula1>INDIRECT(SUBSTITUTE(A4,"-","_")&amp;"update_delete")</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="AA4:AA1048576">
@@ -35462,26 +35414,26 @@
   <sheetData>
     <row r="1" ht="15" spans="1:2">
       <c r="A1" s="16" t="s">
-        <v>2117</v>
+        <v>2109</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>2118</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2119</v>
+        <v>2111</v>
       </c>
       <c r="B2" t="s">
-        <v>2120</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="17" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>2110</v>
+        <v>2114</v>
       </c>
       <c r="F4" s="19">
         <v>1</v>
@@ -35507,10 +35459,10 @@
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="17" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="F5" s="19">
         <v>1</v>
@@ -35536,26 +35488,26 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="17" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="17" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="17" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="F8" s="19">
         <v>1</v>
@@ -35564,10 +35516,10 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="17" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="F9" s="19">
         <v>1</v>
@@ -35592,16 +35544,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1" t="s">
         <v>2121</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2122</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2123</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2124</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -35609,68 +35561,68 @@
         <v>944</v>
       </c>
       <c r="B2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C2" t="s">
         <v>2125</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>2126</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
   </sheetData>
@@ -35702,7 +35654,7 @@
         <v>1377</v>
       </c>
       <c r="C2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="3" ht="15" spans="2:17">
@@ -35710,69 +35662,69 @@
         <v>1387</v>
       </c>
       <c r="C3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D3" t="s">
         <v>2140</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>2141</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>2142</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>2143</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>2144</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>2145</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>2146</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>2147</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>2148</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>2149</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>2150</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>2151</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>2152</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>2153</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>2154</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:7">
       <c r="B4" s="7" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C4" t="s">
         <v>2155</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>2156</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>2157</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2158</v>
       </c>
       <c r="F4" t="s">
         <v>1166</v>
       </c>
       <c r="G4" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:2">
@@ -35783,18 +35735,18 @@
     </row>
     <row r="6" ht="15" spans="2:4">
       <c r="B6" s="8" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C6" t="s">
         <v>2160</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>2161</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="7" ht="15" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C7" t="s">
         <v>1245</v>
@@ -35802,52 +35754,52 @@
     </row>
     <row r="8" ht="15" spans="2:17">
       <c r="B8" s="8" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C8" t="s">
         <v>2164</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>2165</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>2166</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>2167</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>2168</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>2169</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>2170</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>2171</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>2172</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>2173</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>2174</v>
-      </c>
-      <c r="M8" t="s">
-        <v>2175</v>
       </c>
       <c r="N8" t="s">
         <v>1501</v>
       </c>
       <c r="O8" t="s">
+        <v>2175</v>
+      </c>
+      <c r="P8" t="s">
         <v>2176</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>2177</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>2178</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:2">
@@ -35858,13 +35810,13 @@
     </row>
     <row r="10" ht="15" spans="2:5">
       <c r="B10" s="9" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="C10" t="s">
         <v>871</v>
       </c>
       <c r="D10" t="s">
-        <v>2111</v>
+        <v>2179</v>
       </c>
       <c r="E10" t="s">
         <v>2180</v>
@@ -35875,7 +35827,7 @@
         <v>2181</v>
       </c>
       <c r="C11" t="s">
-        <v>2119</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:8">
@@ -39001,43 +38953,43 @@
         <v>2808</v>
       </c>
       <c r="G60" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="H60" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="I60" t="s">
         <v>2809</v>
       </c>
       <c r="J60" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="K60" t="s">
         <v>2810</v>
       </c>
       <c r="L60" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="M60" t="s">
         <v>2811</v>
       </c>
       <c r="N60" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="O60" t="s">
         <v>2812</v>
       </c>
       <c r="P60" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="Q60" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="R60" t="s">
         <v>2813</v>
       </c>
       <c r="S60" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="T60" t="s">
         <v>2814</v>
@@ -39052,16 +39004,16 @@
         <v>2263</v>
       </c>
       <c r="X60" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="Y60" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="Z60" t="s">
         <v>2817</v>
       </c>
       <c r="AA60" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="AB60" t="s">
         <v>2818</v>
@@ -39076,7 +39028,7 @@
         <v>2821</v>
       </c>
       <c r="AF60" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="AG60" t="s">
         <v>2822</v>
@@ -39140,7 +39092,7 @@
         <v>2839</v>
       </c>
       <c r="N62" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="O62" t="s">
         <v>2840</v>
@@ -39211,7 +39163,7 @@
         <v>2839</v>
       </c>
       <c r="N63" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="O63" t="s">
         <v>2840</v>
@@ -39282,7 +39234,7 @@
         <v>2839</v>
       </c>
       <c r="N64" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="O64" t="s">
         <v>2840</v>
@@ -39404,7 +39356,7 @@
         <v>2859</v>
       </c>
       <c r="C68" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D68" t="s">
         <v>2596</v>
@@ -39416,7 +39368,7 @@
         <v>2860</v>
       </c>
       <c r="G68" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H68" t="s">
         <v>2861</v>
@@ -39430,7 +39382,7 @@
         <v>2859</v>
       </c>
       <c r="C69" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D69" t="s">
         <v>2596</v>
@@ -39442,7 +39394,7 @@
         <v>2860</v>
       </c>
       <c r="G69" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H69" t="s">
         <v>2861</v>
@@ -39456,7 +39408,7 @@
         <v>2859</v>
       </c>
       <c r="C70" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D70" t="s">
         <v>2596</v>
@@ -39468,7 +39420,7 @@
         <v>2860</v>
       </c>
       <c r="G70" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H70" t="s">
         <v>2861</v>
@@ -39482,7 +39434,7 @@
         <v>2859</v>
       </c>
       <c r="C71" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D71" t="s">
         <v>2596</v>
@@ -39494,7 +39446,7 @@
         <v>2860</v>
       </c>
       <c r="G71" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H71" t="s">
         <v>2861</v>
@@ -39508,7 +39460,7 @@
         <v>2859</v>
       </c>
       <c r="C72" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D72" t="s">
         <v>2596</v>
@@ -39520,7 +39472,7 @@
         <v>2860</v>
       </c>
       <c r="G72" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H72" t="s">
         <v>2861</v>
@@ -53251,208 +53203,208 @@
     </row>
     <row r="2" spans="2:71">
       <c r="B2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="C2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="D2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="E2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="F2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="G2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="H2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="I2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="J2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="K2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="L2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="M2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="N2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="O2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="P2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Q2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="R2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="S2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="T2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="U2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="W2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="X2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Y2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Z2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AB2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AC2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AD2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AE2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AF2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AG2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AH2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AI2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AJ2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AK2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AL2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AM2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AN2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AO2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AP2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AQ2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AR2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AS2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AT2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AU2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AV2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AW2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AX2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AY2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="AZ2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BA2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BB2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BC2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BD2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BE2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BF2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BG2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BH2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BI2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BJ2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BK2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BL2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BM2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BN2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BO2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BP2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BQ2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BR2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="BS2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="3" spans="1:71">
@@ -53672,7 +53624,7 @@
     </row>
     <row r="4" spans="1:71">
       <c r="A4" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B4" t="s">
         <v>944</v>
@@ -53690,7 +53642,7 @@
         <v>2826</v>
       </c>
       <c r="G4" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="H4" t="s">
         <v>944</v>
@@ -53750,7 +53702,7 @@
         <v>2864</v>
       </c>
       <c r="AA4" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="AB4" t="s">
         <v>1198</v>
@@ -53780,7 +53732,7 @@
         <v>2439</v>
       </c>
       <c r="AK4" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="AL4" t="s">
         <v>2429</v>
@@ -53792,7 +53744,7 @@
         <v>3806</v>
       </c>
       <c r="AO4" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="AP4" t="s">
         <v>3782</v>
@@ -53855,7 +53807,7 @@
         <v>2006</v>
       </c>
       <c r="BJ4" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="BK4" t="s">
         <v>2439</v>
@@ -53882,7 +53834,7 @@
         <v>2213</v>
       </c>
       <c r="BS4" t="s">
-        <v>2119</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="5" spans="2:70">
@@ -53902,13 +53854,13 @@
         <v>2827</v>
       </c>
       <c r="G5" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="H5" t="s">
         <v>653</v>
       </c>
       <c r="I5" t="s">
-        <v>2111</v>
+        <v>2179</v>
       </c>
       <c r="J5" t="s">
         <v>2197</v>
@@ -53959,7 +53911,7 @@
         <v>2865</v>
       </c>
       <c r="AA5" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="AB5" t="s">
         <v>1710</v>
@@ -53986,7 +53938,7 @@
         <v>2440</v>
       </c>
       <c r="AK5" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="AL5" t="s">
         <v>2430</v>
@@ -54061,7 +54013,7 @@
         <v>3804</v>
       </c>
       <c r="BJ5" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="BK5" t="s">
         <v>2440</v>
@@ -54099,7 +54051,7 @@
         <v>2828</v>
       </c>
       <c r="G6" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="I6" t="s">
         <v>2180</v>
@@ -54150,7 +54102,7 @@
         <v>2866</v>
       </c>
       <c r="AA6" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="AB6" t="s">
         <v>2491</v>
@@ -54177,7 +54129,7 @@
         <v>2441</v>
       </c>
       <c r="AK6" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="AL6" t="s">
         <v>2431</v>
@@ -54260,7 +54212,7 @@
         <v>2381</v>
       </c>
       <c r="G7" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="J7" t="s">
         <v>2199</v>
@@ -54308,7 +54260,7 @@
         <v>2867</v>
       </c>
       <c r="AA7" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="AB7" t="s">
         <v>2492</v>
@@ -54412,7 +54364,7 @@
         <v>1565</v>
       </c>
       <c r="G8" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="J8" t="s">
         <v>2200</v>
@@ -54460,7 +54412,7 @@
         <v>2868</v>
       </c>
       <c r="AA8" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="AB8" t="s">
         <v>2493</v>
@@ -54487,7 +54439,7 @@
         <v>2443</v>
       </c>
       <c r="AK8" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="AL8" t="s">
         <v>2433</v>
@@ -54499,10 +54451,10 @@
         <v>1178</v>
       </c>
       <c r="AO8" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="AR8" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="AS8" t="s">
         <v>2493</v>
@@ -54564,7 +54516,7 @@
         <v>2382</v>
       </c>
       <c r="G9" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="J9" t="s">
         <v>2201</v>
@@ -54612,7 +54564,7 @@
         <v>2869</v>
       </c>
       <c r="AA9" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="AB9" t="s">
         <v>2494</v>
@@ -54651,7 +54603,7 @@
         <v>2861</v>
       </c>
       <c r="AR9" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="AS9" t="s">
         <v>2494</v>
@@ -54713,7 +54665,7 @@
         <v>2383</v>
       </c>
       <c r="G10" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="J10" t="s">
         <v>2202</v>
@@ -54758,7 +54710,7 @@
         <v>2870</v>
       </c>
       <c r="AA10" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="AB10" t="s">
         <v>1671</v>
@@ -54859,7 +54811,7 @@
         <v>2384</v>
       </c>
       <c r="G11" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="J11" t="s">
         <v>1509</v>
@@ -54895,7 +54847,7 @@
         <v>2871</v>
       </c>
       <c r="AA11" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="AC11" t="s">
         <v>2340</v>
@@ -54925,7 +54877,7 @@
         <v>3812</v>
       </c>
       <c r="AR11" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="AU11" t="s">
         <v>2502</v>
@@ -54972,7 +54924,7 @@
         <v>2385</v>
       </c>
       <c r="G12" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="J12" t="s">
         <v>2203</v>
@@ -55005,7 +54957,7 @@
         <v>2872</v>
       </c>
       <c r="AA12" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="AC12" t="s">
         <v>2341</v>
@@ -55076,7 +55028,7 @@
         <v>2386</v>
       </c>
       <c r="G13" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="J13" t="s">
         <v>2204</v>
@@ -55106,7 +55058,7 @@
         <v>2873</v>
       </c>
       <c r="AA13" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="AC13" t="s">
         <v>2342</v>
@@ -55127,7 +55079,7 @@
         <v>1639</v>
       </c>
       <c r="AR13" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="AU13" t="s">
         <v>2504</v>
@@ -55168,7 +55120,7 @@
         <v>2387</v>
       </c>
       <c r="G14" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="J14" t="s">
         <v>2205</v>
@@ -55195,7 +55147,7 @@
         <v>2874</v>
       </c>
       <c r="AA14" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="AC14" t="s">
         <v>2343</v>
@@ -55266,7 +55218,7 @@
         <v>2446</v>
       </c>
       <c r="S15" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="T15" t="s">
         <v>2446</v>
@@ -55278,7 +55230,7 @@
         <v>2875</v>
       </c>
       <c r="AA15" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="AC15" t="s">
         <v>2344</v>
@@ -55293,7 +55245,7 @@
         <v>2446</v>
       </c>
       <c r="AR15" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="AU15" t="s">
         <v>2506</v>
@@ -55328,7 +55280,7 @@
         <v>2389</v>
       </c>
       <c r="G16" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="J16" t="s">
         <v>2207</v>
@@ -55355,7 +55307,7 @@
         <v>2876</v>
       </c>
       <c r="AA16" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="AC16" t="s">
         <v>2345</v>
@@ -55402,7 +55354,7 @@
         <v>2528</v>
       </c>
       <c r="G17" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="J17" t="s">
         <v>2208</v>
@@ -55429,7 +55381,7 @@
         <v>2877</v>
       </c>
       <c r="AA17" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="AC17" t="s">
         <v>2346</v>
@@ -55444,7 +55396,7 @@
         <v>2448</v>
       </c>
       <c r="AR17" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="AY17" t="s">
         <v>2448</v>
@@ -55473,7 +55425,7 @@
         <v>2529</v>
       </c>
       <c r="G18" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="J18" t="s">
         <v>2209</v>
@@ -55500,7 +55452,7 @@
         <v>2878</v>
       </c>
       <c r="AA18" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="AC18" t="s">
         <v>2347</v>
@@ -55515,7 +55467,7 @@
         <v>2449</v>
       </c>
       <c r="AR18" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="AY18" t="s">
         <v>2449</v>
@@ -55594,7 +55546,7 @@
         <v>2349</v>
       </c>
       <c r="AR20" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="BH20" t="s">
         <v>2300</v>
@@ -55739,7 +55691,7 @@
         <v>2353</v>
       </c>
       <c r="AR25" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="BH25" t="s">
         <v>2305</v>
@@ -55762,7 +55714,7 @@
         <v>2354</v>
       </c>
       <c r="AR26" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="BH26" t="s">
         <v>2306</v>
@@ -55808,7 +55760,7 @@
         <v>2356</v>
       </c>
       <c r="AR28" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="BH28" t="s">
         <v>2308</v>
@@ -55908,7 +55860,7 @@
         <v>2361</v>
       </c>
       <c r="AR33" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="BH33" t="s">
         <v>2313</v>
@@ -60946,7 +60898,7 @@
         <v>1474</v>
       </c>
       <c r="B1" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -61314,7 +61266,7 @@
         <v>1474</v>
       </c>
       <c r="B47" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -62666,7 +62618,7 @@
         <v>1474</v>
       </c>
       <c r="B216" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
   </sheetData>
